--- a/data/trans_orig/IP16B03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B03-Edad-trans_orig.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
